--- a/manufacturing_forms/023_manufacturing_skilled_worker_job_application--manufacturing_forms.xlsx
+++ b/manufacturing_forms/023_manufacturing_skilled_worker_job_application--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_1_year',_'value':_1}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 1 year', 'value': 1}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1_year_or_more',_'value':_2}</t>
+          <t>1_year_or_more</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1 year or more', 'value': 2}</t>
+          <t>1 year or more</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_applicable',_'value':_3}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Applicable', 'value': 3}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school_diploma_or_equivalent',_'value':_1}</t>
+          <t>high_school_diploma_or_equivalent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School Diploma or Equivalent', 'value': 1}</t>
+          <t>High School Diploma or Equivalent</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"associate's_degree_or_equivalent",_'value':_2}</t>
+          <t>associate's_degree_or_equivalent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "Associate's Degree or Equivalent", 'value': 2}</t>
+          <t>Associate's Degree or Equivalent</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_"bachelor's_degree_or_equivalent",_'value':_3}</t>
+          <t>bachelor's_degree_or_equivalent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': "Bachelor's Degree or Equivalent", 'value': 3}</t>
+          <t>Bachelor's Degree or Equivalent</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_"master's_degree_or_equivalent",_'value':_4}</t>
+          <t>master's_degree_or_equivalent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': "Master's Degree or Equivalent", 'value': 4}</t>
+          <t>Master's Degree or Equivalent</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'doctoral_degree_or_equivalent',_'value':_5}</t>
+          <t>doctoral_degree_or_equivalent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Doctoral Degree or Equivalent', 'value': 5}</t>
+          <t>Doctoral Degree or Equivalent</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other',_'value':_6}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other', 'value': 6}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_active',_'value':_'not_active'}</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Active', 'value': 'not_active'}</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'on_leave',_'value':_'on_leave'}</t>
+          <t>on_leave</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'On Leave', 'value': 'on_leave'}</t>
+          <t>On Leave</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'retired',_'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Retired', 'value': 'retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'resigned',_'value':_'resigned'}</t>
+          <t>resigned</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Resigned', 'value': 'resigned'}</t>
+          <t>Resigned</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manufacturing',_'value':_'manufacturing'}</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manufacturing', 'value': 'manufacturing'}</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'production',_'value':_'production'}</t>
+          <t>production</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Production', 'value': 'production'}</t>
+          <t>Production</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'warehouse',_'value':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Warehouse', 'value': 'warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'day_shift',_'value':_'day'}</t>
+          <t>day_shift</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Day Shift', 'value': 'day'}</t>
+          <t>Day Shift</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'evening_shift',_'value':_'evening'}</t>
+          <t>evening_shift</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Evening Shift', 'value': 'evening'}</t>
+          <t>Evening Shift</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'night_shift',_'value':_'night'}</t>
+          <t>night_shift</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Night Shift', 'value': 'night'}</t>
+          <t>Night Shift</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rotating_shifts',_'value':_'rotating'}</t>
+          <t>rotating_shifts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rotating Shifts', 'value': 'rotating'}</t>
+          <t>Rotating Shifts</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'on_call',_'value':_'on_call'}</t>
+          <t>on_call</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'On Call', 'value': 'on_call'}</t>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
